--- a/artfynd/A 63257-2023 artfynd.xlsx
+++ b/artfynd/A 63257-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63257-2023 artfynd.xlsx
+++ b/artfynd/A 63257-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1797,934 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114922418</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>718012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7060782</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114922411</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>718069</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7060677</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114922421</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79023</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>718017</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7060776</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114922415</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>718003</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7061199</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114922419</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78196</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>718012</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7060782</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114922412</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5476</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>718020</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7060961</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114922413</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>718005</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7061086</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114922420</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78195</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>718012</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7060782</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114922414</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>717980</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7061119</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
